--- a/src/pandorafits/formats/level3/level3-headers.xlsx
+++ b/src/pandorafits/formats/level3/level3-headers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindseywiser/Desktop/Pandora/pandora-fits-main/src/pandorafits/formats/level3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/level3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD0DDC0-F011-4544-BAFB-5B2D59C4C0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F6120A-168F-FC4B-A37B-B3BDB4873C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Primary" sheetId="1" r:id="rId1"/>
